--- a/Mebra/MIRALEDO_Analiza_Ambalaje_MEBRA.xlsx
+++ b/Mebra/MIRALEDO_Analiza_Ambalaje_MEBRA.xlsx
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C21" s="130" t="inlineStr">
         <is>
-          <t>46 produse pe mebra.ro (37 individuale + 9 seturi), 28.10.2026; 15 unitati de ambalaj identificate pana acum</t>
+          <t>46 produse pe mebra.ro (37 individuale + 9 seturi), 28.10.2026; 19 unitati de ambalaj identificate</t>
         </is>
       </c>
       <c r="D21" s="131" t="n"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F9" s="133" t="inlineStr">
         <is>
-          <t>MEBRA Ulei de masaj antistres 300ml; MEBRA ulei de masaj revitalizant 300ml</t>
+          <t>MEBRA Ulei de masaj antistres 300ml; MEBRA ulei de masaj revitalizant 300ml; KIT drenaj limfatic, venotonic (set)</t>
         </is>
       </c>
       <c r="G9" s="132" t="n"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="F11" s="133" t="inlineStr">
         <is>
-          <t>MEBRA Ulei vitaminizant copii 150ml</t>
+          <t>MEBRA Ulei vitaminizant copii 150ml; Set complet îngrijire bebeluși (set)</t>
         </is>
       </c>
       <c r="G11" s="132" t="n"/>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F12" s="133" t="inlineStr">
         <is>
-          <t>ERITROACNOL loțiune 120ml</t>
+          <t>ERITROACNOL loțiune 120ml; KIT ten gras și acneic – extracte de plante (set)</t>
         </is>
       </c>
       <c r="G12" s="132" t="n"/>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="C13" s="133" t="inlineStr">
         <is>
-          <t>Flacon 100 ml + spray + capac</t>
+          <t>Flacon 100 ml transparent + spray + capac</t>
         </is>
       </c>
       <c r="D13" s="133" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="E13" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Transparent (flacon), alb (spray si capac), din poza</t>
         </is>
       </c>
       <c r="F13" s="133" t="inlineStr">
         <is>
-          <t>MEBRA Solutie curatare maini 100ml; MEBRA loțiune pentru picioare 100 ml; TONIFOR loțiune tonică 100ml</t>
+          <t>MEBRA Solutie curatare maini 100ml; KIT Protecție mâini + anti piele uscată (set)</t>
         </is>
       </c>
       <c r="G13" s="132" t="n"/>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="C14" s="133" t="inlineStr">
         <is>
-          <t>Flacon 50 ml + spray + capac</t>
+          <t>Flacon 100 ml alb + spray + capac</t>
         </is>
       </c>
       <c r="D14" s="133" t="inlineStr">
         <is>
-          <t>50 ml</t>
+          <t>100 ml</t>
         </is>
       </c>
       <c r="E14" s="133" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="F14" s="133" t="inlineStr">
         <is>
-          <t>MEBRA spray propolis și gălbenele 50ml; MEBRA spray propolis și coada șoricelului 50ml</t>
+          <t>MEBRA loțiune pentru picioare 100 ml; TONIFOR loțiune tonică 100ml; Set complet îngrijire picioare (set); KIT anti dureri musculare (set)</t>
         </is>
       </c>
       <c r="G14" s="132" t="n"/>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="C15" s="133" t="inlineStr">
         <is>
-          <t>Recipient pudra 75 g + capac</t>
+          <t>Flacon 50 ml + spray + capac</t>
         </is>
       </c>
       <c r="D15" s="133" t="inlineStr">
         <is>
-          <t>75 g</t>
+          <t>50 ml</t>
         </is>
       </c>
       <c r="E15" s="133" t="inlineStr">
         <is>
-          <t>Alb (recipient), capac colorat dupa produs, din poza</t>
+          <t>Alb (din poza)</t>
         </is>
       </c>
       <c r="F15" s="133" t="inlineStr">
         <is>
-          <t>MEBRA Pudră fructată 75g; MEBRA pudră mentolată 75g; MEBRA pudră propolis 75 g; MEBRA pudră mentolată împotriva transpirației 75 g; MEBRA pudră pentru copii cu portocale și cătină 75g</t>
+          <t>MEBRA spray propolis și gălbenele 50ml; MEBRA spray propolis și coada șoricelului 50ml; KIT ajutor rapid răni (set)</t>
         </is>
       </c>
       <c r="G15" s="132" t="n"/>
@@ -2587,22 +2587,22 @@
       </c>
       <c r="C16" s="133" t="inlineStr">
         <is>
-          <t>Borcan 45 ml + capac</t>
+          <t>Flacon 30 ml + spray (plastic sau sticla, in cutie)</t>
         </is>
       </c>
       <c r="D16" s="133" t="inlineStr">
         <is>
-          <t>45 ml</t>
+          <t>30 ml</t>
         </is>
       </c>
       <c r="E16" s="133" t="inlineStr">
         <is>
-          <t>Alb (borcan), capac galben / verde / rosu dupa produs, din poza</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F16" s="133" t="inlineStr">
         <is>
-          <t>MEBRA cremă cu gheara diavolului 45ml; MEBRA crema cu TATANEASA 45 ml; MEBRA cremă cu vitamina A 45ml</t>
+          <t>SALVO-MEB spray 30ml; Set sănătatea tractului respirator (set)</t>
         </is>
       </c>
       <c r="G16" s="132" t="n"/>
@@ -2632,22 +2632,22 @@
       </c>
       <c r="C17" s="133" t="inlineStr">
         <is>
-          <t>Tub 100 ml + capac</t>
+          <t>Flacon 30 ml + capac (plastic sau sticla, in cutie)</t>
         </is>
       </c>
       <c r="D17" s="133" t="inlineStr">
         <is>
-          <t>100 ml</t>
+          <t>30 ml</t>
         </is>
       </c>
       <c r="E17" s="133" t="inlineStr">
         <is>
-          <t>Alb (tub), capac rosu / galben dupa produs, din poza</t>
+          <t>De confirmat</t>
         </is>
       </c>
       <c r="F17" s="133" t="inlineStr">
         <is>
-          <t>MEBRA cremă cu vitamina A 100ml; MEBRA cremă cu extract de gălbenele 100 ml</t>
+          <t>MEBRA TINCTURĂ PROPOLIS 30 % – supliment alimentar 30 ml; Set sănătatea tractului respirator (set)</t>
         </is>
       </c>
       <c r="G17" s="132" t="n"/>
@@ -2677,22 +2677,22 @@
       </c>
       <c r="C18" s="133" t="inlineStr">
         <is>
-          <t>Tub 75 ml + capac mare (tub asezat pe capac)</t>
+          <t>Recipient pudra 75 g + capac</t>
         </is>
       </c>
       <c r="D18" s="133" t="inlineStr">
         <is>
-          <t>75 ml</t>
+          <t>75 g</t>
         </is>
       </c>
       <c r="E18" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Alb (recipient), capac colorat dupa produs, din poza</t>
         </is>
       </c>
       <c r="F18" s="133" t="inlineStr">
         <is>
-          <t>ERITROACNOL cremă 75ml; ERITROACNOL gel 75ml</t>
+          <t>MEBRA Pudră fructată 75g; MEBRA pudră mentolată 75g; MEBRA pudră propolis 75 g; MEBRA pudră mentolată împotriva transpirației 75 g; MEBRA pudră pentru copii cu portocale și cătină 75g; Set complet îngrijire bebeluși (set)</t>
         </is>
       </c>
       <c r="G18" s="132" t="n"/>
@@ -2722,22 +2722,22 @@
       </c>
       <c r="C19" s="133" t="inlineStr">
         <is>
-          <t>Tub 75 ml + capac</t>
+          <t>Borcan 45 ml + capac</t>
         </is>
       </c>
       <c r="D19" s="133" t="inlineStr">
         <is>
-          <t>75 ml</t>
+          <t>45 ml</t>
         </is>
       </c>
       <c r="E19" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Alb (borcan), capac galben / verde / rosu dupa produs, din poza</t>
         </is>
       </c>
       <c r="F19" s="133" t="inlineStr">
         <is>
-          <t>MEBRA balsam pentru picioare obosite 75ml; TONIFOR cremă tonică și relaxantă 75ml; MEBRA crema cu extract de CASTANE 75ml; TONIFOR arnica gel 75ml</t>
+          <t>MEBRA cremă cu gheara diavolului 45ml; MEBRA crema cu TATANEASA 45 ml; MEBRA cremă cu vitamina A 45ml; MEDARA cremă cu vitaminele A și E 45 ml (pe site doar cutia, borcanul de confirmat); KIT îngrijire iarnă, piele ultra uscată (set)</t>
         </is>
       </c>
       <c r="G19" s="132" t="n"/>
@@ -2767,22 +2767,22 @@
       </c>
       <c r="C20" s="133" t="inlineStr">
         <is>
-          <t>Tub 40 ml + capac</t>
+          <t>Tub 100 ml + capac</t>
         </is>
       </c>
       <c r="D20" s="133" t="inlineStr">
         <is>
-          <t>40 ml</t>
+          <t>100 ml</t>
         </is>
       </c>
       <c r="E20" s="133" t="inlineStr">
         <is>
-          <t>Alb (din poza)</t>
+          <t>Alb (tub), capac rosu / galben dupa produs, din poza</t>
         </is>
       </c>
       <c r="F20" s="133" t="inlineStr">
         <is>
-          <t>MEBRA cremă cu vitamina A 40ml; MEBRA Cremă îngrijire călcâie 40ml</t>
+          <t>MEBRA cremă cu vitamina A 100ml; MEBRA cremă cu extract de gălbenele 100 ml</t>
         </is>
       </c>
       <c r="G20" s="132" t="n"/>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="C21" s="133" t="inlineStr">
         <is>
-          <t>Recipient aerosol 59,5 g + valva + capac (in cutie)</t>
+          <t>Tub 75 ml + capac mare (tub asezat pe capac)</t>
         </is>
       </c>
       <c r="D21" s="133" t="inlineStr">
         <is>
-          <t>59,5 g</t>
+          <t>75 ml</t>
         </is>
       </c>
       <c r="E21" s="133" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F21" s="133" t="inlineStr">
         <is>
-          <t>OXIMED Spray cutanat 59,5g</t>
+          <t>ERITROACNOL cremă 75ml; ERITROACNOL gel 75ml; KIT ten gras și acneic – extracte de plante (set)</t>
         </is>
       </c>
       <c r="G21" s="132" t="n"/>
@@ -2851,79 +2851,255 @@
       </c>
       <c r="M21" s="138" t="n"/>
     </row>
-    <row r="22" s="128"/>
-    <row r="23" s="128"/>
-    <row r="24" ht="19.95" customHeight="1" s="128">
-      <c r="C24" s="76" t="inlineStr">
+    <row r="22" s="128">
+      <c r="B22" s="132" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" s="133" t="inlineStr">
+        <is>
+          <t>Tub 75 ml + capac</t>
+        </is>
+      </c>
+      <c r="D22" s="133" t="inlineStr">
+        <is>
+          <t>75 ml</t>
+        </is>
+      </c>
+      <c r="E22" s="133" t="inlineStr">
+        <is>
+          <t>Alb (din poza)</t>
+        </is>
+      </c>
+      <c r="F22" s="133" t="inlineStr">
+        <is>
+          <t>MEBRA balsam pentru picioare obosite 75ml; TONIFOR cremă tonică și relaxantă 75ml; MEBRA crema cu extract de CASTANE 75ml; TONIFOR arnica gel 75ml; Set complet îngrijire picioare (set); KIT drenaj limfatic, venotonic (set); KIT anti dureri musculare (set)</t>
+        </is>
+      </c>
+      <c r="G22" s="132" t="n"/>
+      <c r="H22" s="134">
+        <f>IFERROR(INDIRECT("'"&amp;G22&amp;"'!E26"),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="135">
+        <f>IFERROR(INDIRECT("'"&amp;G22&amp;"'!E27"),"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="136">
+        <f>IFERROR(INDIRECT("'"&amp;G22&amp;"'!E28"),"")</f>
+        <v/>
+      </c>
+      <c r="K22" s="137" t="n"/>
+      <c r="L22" s="137" t="inlineStr">
+        <is>
+          <t>In curs</t>
+        </is>
+      </c>
+      <c r="M22" s="138" t="n"/>
+    </row>
+    <row r="23" s="128">
+      <c r="B23" s="132" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" s="133" t="inlineStr">
+        <is>
+          <t>Tub 40 ml + capac</t>
+        </is>
+      </c>
+      <c r="D23" s="133" t="inlineStr">
+        <is>
+          <t>40 ml</t>
+        </is>
+      </c>
+      <c r="E23" s="133" t="inlineStr">
+        <is>
+          <t>Alb (din poza)</t>
+        </is>
+      </c>
+      <c r="F23" s="133" t="inlineStr">
+        <is>
+          <t>MEBRA cremă cu vitamina A 40ml; MEBRA Cremă îngrijire călcâie 40ml; KIT Protecție mâini + anti piele uscată (set); KIT îngrijire iarnă, piele ultra uscată (set)</t>
+        </is>
+      </c>
+      <c r="G23" s="132" t="n"/>
+      <c r="H23" s="134">
+        <f>IFERROR(INDIRECT("'"&amp;G23&amp;"'!E26"),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="135">
+        <f>IFERROR(INDIRECT("'"&amp;G23&amp;"'!E27"),"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="136">
+        <f>IFERROR(INDIRECT("'"&amp;G23&amp;"'!E28"),"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="137" t="n"/>
+      <c r="L23" s="137" t="inlineStr">
+        <is>
+          <t>In curs</t>
+        </is>
+      </c>
+      <c r="M23" s="138" t="n"/>
+    </row>
+    <row r="24" s="128">
+      <c r="B24" s="132" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="133" t="inlineStr">
+        <is>
+          <t>Plic individual pansament 19x72 mm (in cutie)</t>
+        </is>
+      </c>
+      <c r="D24" s="133" t="inlineStr">
+        <is>
+          <t>De confirmat</t>
+        </is>
+      </c>
+      <c r="E24" s="133" t="inlineStr">
+        <is>
+          <t>Alb cu imprimare rosie (din poza)</t>
+        </is>
+      </c>
+      <c r="F24" s="133" t="inlineStr">
+        <is>
+          <t>Pansament rezistent la apa 207M, 1.9 cm*7.2 cm set 20 bucati; KIT ajutor rapid răni (set)</t>
+        </is>
+      </c>
+      <c r="G24" s="132" t="n"/>
+      <c r="H24" s="134">
+        <f>IFERROR(INDIRECT("'"&amp;G24&amp;"'!E26"),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="135">
+        <f>IFERROR(INDIRECT("'"&amp;G24&amp;"'!E27"),"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="136">
+        <f>IFERROR(INDIRECT("'"&amp;G24&amp;"'!E28"),"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="137" t="n"/>
+      <c r="L24" s="137" t="inlineStr">
+        <is>
+          <t>In curs</t>
+        </is>
+      </c>
+      <c r="M24" s="138" t="n"/>
+    </row>
+    <row r="25" s="128">
+      <c r="B25" s="132" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="133" t="inlineStr">
+        <is>
+          <t>Recipient aerosol 59,5 g + valva + capac (in cutie)</t>
+        </is>
+      </c>
+      <c r="D25" s="133" t="inlineStr">
+        <is>
+          <t>59,5 g</t>
+        </is>
+      </c>
+      <c r="E25" s="133" t="inlineStr">
+        <is>
+          <t>Alb (din poza)</t>
+        </is>
+      </c>
+      <c r="F25" s="133" t="inlineStr">
+        <is>
+          <t>OXIMED Spray cutanat 59,5g</t>
+        </is>
+      </c>
+      <c r="G25" s="132" t="n"/>
+      <c r="H25" s="134">
+        <f>IFERROR(INDIRECT("'"&amp;G25&amp;"'!E26"),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="135">
+        <f>IFERROR(INDIRECT("'"&amp;G25&amp;"'!E27"),"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="136">
+        <f>IFERROR(INDIRECT("'"&amp;G25&amp;"'!E28"),"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="137" t="n"/>
+      <c r="L25" s="137" t="inlineStr">
+        <is>
+          <t>In curs</t>
+        </is>
+      </c>
+      <c r="M25" s="138" t="n"/>
+    </row>
+    <row r="26" s="128"/>
+    <row r="27" s="128"/>
+    <row r="28" ht="19.95" customHeight="1" s="128">
+      <c r="C28" s="76" t="inlineStr">
         <is>
           <t>Rezumat (automat)</t>
         </is>
       </c>
-      <c r="D24" s="73" t="inlineStr">
+      <c r="D28" s="73" t="inlineStr">
         <is>
           <t>Nr. unitati</t>
         </is>
-      </c>
-    </row>
-    <row r="25" ht="19.95" customHeight="1" s="128">
-      <c r="C25" s="74" t="inlineStr">
-        <is>
-          <t>Unitati analizate</t>
-        </is>
-      </c>
-      <c r="D25" s="75">
-        <f>COUNTIF(G7:G21,"?*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="19.95" customHeight="1" s="128">
-      <c r="C26" s="74" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D26" s="75">
-        <f>COUNTIF($J$7:$J$21,C26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="19.95" customHeight="1" s="128">
-      <c r="C27" s="74" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D27" s="75">
-        <f>COUNTIF($J$7:$J$21,C27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="19.95" customHeight="1" s="128">
-      <c r="C28" s="74" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D28" s="75">
-        <f>COUNTIF($J$7:$J$21,C28)</f>
-        <v/>
       </c>
     </row>
     <row r="29" ht="19.95" customHeight="1" s="128">
       <c r="C29" s="74" t="inlineStr">
         <is>
+          <t>Unitati analizate</t>
+        </is>
+      </c>
+      <c r="D29" s="75">
+        <f>COUNTIF(G7:G25,"?*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="19.95" customHeight="1" s="128">
+      <c r="C30" s="74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D30" s="75">
+        <f>COUNTIF($J$7:$J$25,C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="19.95" customHeight="1" s="128">
+      <c r="C31" s="74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D31" s="75">
+        <f>COUNTIF($J$7:$J$25,C31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="19.95" customHeight="1" s="128">
+      <c r="C32" s="74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D32" s="75">
+        <f>COUNTIF($J$7:$J$25,C32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="19.95" customHeight="1" s="128">
+      <c r="C33" s="74" t="inlineStr">
+        <is>
           <t>Sub 70% - nereciclabil</t>
         </is>
       </c>
-      <c r="D29" s="75">
-        <f>COUNTIF($J$7:$J$21,C29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
+      <c r="D33" s="75">
+        <f>COUNTIF($J$7:$J$25,C33)</f>
+        <v/>
+      </c>
+    </row>
     <row r="34"/>
     <row r="35"/>
     <row r="36"/>
@@ -2935,12 +3111,12 @@
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G7:G21">
+  <conditionalFormatting sqref="G7:G25">
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>AND($G7&lt;&gt;"",$H7="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J21">
+  <conditionalFormatting sqref="J7:J25">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>OR($J7="A",$J7="B")</formula>
     </cfRule>
@@ -2952,10 +3128,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K7:K21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Prioritate" error="Alegeti: Mare, Medie sau Mica." type="list">
+    <dataValidation sqref="K7:K25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Prioritate" error="Alegeti: Mare, Medie sau Mica." type="list">
       <formula1>"Mare,Medie,Mica"</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Stadiu analiza" error="Valoarea nu este in lista. Puteti continua daca este intentionat." type="list" errorStyle="information">
+    <dataValidation sqref="L7:L25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Stadiu analiza" error="Valoarea nu este in lista. Puteti continua daca este intentionat." type="list" errorStyle="information">
       <formula1>"Identificata,In completare,Completa,Oferta trimisa"</formula1>
     </dataValidation>
   </dataValidations>
